--- a/data/trans_bre/P6906-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 18,51</t>
+          <t>-28,04; 17,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 19,16</t>
+          <t>-31,33; 18,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 29,09</t>
+          <t>-11,8; 29,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 40,35</t>
+          <t>-15,88; 35,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,83; 74,04</t>
+          <t>-64,65; 73,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 53,25</t>
+          <t>-56,63; 52,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 111,99</t>
+          <t>-25,18; 111,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 402,47</t>
+          <t>-44,25; 332,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 13,63</t>
+          <t>-22,54; 12,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 10,65</t>
+          <t>-26,41; 11,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 27,26</t>
+          <t>-3,93; 26,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 26,39</t>
+          <t>-14,45; 26,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 93,73</t>
+          <t>-73,2; 86,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 55,85</t>
+          <t>-73,51; 74,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 267,59</t>
+          <t>-24,4; 255,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 193,08</t>
+          <t>-36,35; 186,4</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 17,56</t>
+          <t>-22,44; 17,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 28,95</t>
+          <t>-24,34; 28,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 45,77</t>
+          <t>-8,11; 45,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 23,61</t>
+          <t>-4,77; 23,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 302,04</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-70,32; 186,37</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-69,29; 216,51</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 287,79</t>
+          <t>-26,0; 305,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 8,0</t>
+          <t>-25,22; 8,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 29,94</t>
+          <t>-18,32; 27,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 21,57</t>
+          <t>-30,19; 20,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 12,22</t>
+          <t>-41,01; 15,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,59</t>
+          <t>-100,0; 75,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 153,59</t>
+          <t>-46,03; 122,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 66,63</t>
+          <t>-50,58; 69,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,58; 58,99</t>
+          <t>-84,16; 82,69</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 47,0</t>
+          <t>-16,39; 48,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 52,82</t>
+          <t>-5,66; 53,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 51,12</t>
+          <t>-45,39; 53,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 12,11</t>
+          <t>-20,2; 11,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 514,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 515,37</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 20,29</t>
+          <t>-25,55; 22,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 47,6</t>
+          <t>-5,99; 47,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,75; 83,99</t>
+          <t>12,46; 84,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 25,91</t>
+          <t>-7,82; 25,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,41</t>
+          <t>-100,0; 289,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 577,16</t>
+          <t>-35,07; 585,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,96; —</t>
+          <t>16,48; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 344,14</t>
+          <t>-36,25; 352,36</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 25,35</t>
+          <t>-5,89; 27,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 21,88</t>
+          <t>-12,78; 21,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 22,05</t>
+          <t>-8,27; 22,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 27,16</t>
+          <t>0,11; 27,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 205,33</t>
+          <t>-29,07; 208,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 156,91</t>
+          <t>-40,81; 138,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 177,1</t>
+          <t>-35,43; 190,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 273,27</t>
+          <t>0,09; 253,43</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 18,24</t>
+          <t>-14,07; 17,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 35,41</t>
+          <t>-10,15; 33,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 20,89</t>
+          <t>-30,42; 18,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 18,3</t>
+          <t>-6,97; 16,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 81,03</t>
+          <t>-43,88; 81,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 488,99</t>
+          <t>-55,9; 449,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 102,1</t>
+          <t>-82,54; 111,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 534,94</t>
+          <t>-49,44; 527,01</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,66</t>
+          <t>-7,47; 6,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 12,51</t>
+          <t>-4,43; 12,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 17,14</t>
+          <t>0,83; 16,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 12,86</t>
+          <t>-2,77; 12,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 28,61</t>
+          <t>-29,74; 33,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 54,22</t>
+          <t>-14,58; 53,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 81,76</t>
+          <t>2,24; 80,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 82,42</t>
+          <t>-11,65; 80,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6906-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,09</t>
+          <t>15,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 17,37</t>
+          <t>-31,59; 15,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 18,35</t>
+          <t>-31,53; 18,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 29,1</t>
+          <t>-11,93; 31,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 35,85</t>
+          <t>-8,59; 40,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 73,24</t>
+          <t>-68,81; 71,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 52,64</t>
+          <t>-54,32; 52,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 111,23</t>
+          <t>-25,29; 124,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 332,36</t>
+          <t>-38,69; 535,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 12,37</t>
+          <t>-22,13; 12,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 11,66</t>
+          <t>-28,65; 10,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 26,88</t>
+          <t>-3,21; 26,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 26,83</t>
+          <t>-18,49; 23,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 86,34</t>
+          <t>-74,97; 68,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,51; 74,22</t>
+          <t>-72,87; 53,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 255,34</t>
+          <t>-23,09; 266,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 186,4</t>
+          <t>-40,37; 130,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 17,22</t>
+          <t>-22,43; 18,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 28,69</t>
+          <t>-26,54; 27,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 45,24</t>
+          <t>-8,13; 45,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 23,07</t>
+          <t>-4,88; 23,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 302,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 186,37</t>
+          <t>-70,9; 197,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 305,87</t>
+          <t>-25,11; 293,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,6</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-31,79%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 8,19</t>
+          <t>-24,12; 9,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 27,38</t>
+          <t>-18,1; 27,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 20,88</t>
+          <t>-29,23; 21,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 15,25</t>
+          <t>-21,03; 22,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,13</t>
+          <t>-100,0; 125,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 122,46</t>
+          <t>-46,41; 132,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 69,78</t>
+          <t>-50,07; 64,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,16; 82,69</t>
+          <t>-42,2; 121,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-19,12%</t>
+          <t>-1,96%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 48,6</t>
+          <t>-16,62; 50,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 53,63</t>
+          <t>-5,76; 54,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 53,69</t>
+          <t>-40,4; 53,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 11,71</t>
+          <t>-16,39; 13,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 514,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 515,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,6</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 22,18</t>
+          <t>-26,45; 23,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 47,35</t>
+          <t>-6,67; 44,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,46; 84,79</t>
+          <t>13,76; 86,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 25,46</t>
+          <t>-7,86; 25,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 289,81</t>
+          <t>-100,0; 201,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 585,01</t>
+          <t>-38,71; 592,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,48; —</t>
+          <t>26,34; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 352,36</t>
+          <t>-35,34; 386,38</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 27,27</t>
+          <t>-6,72; 24,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 21,6</t>
+          <t>-13,98; 22,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 22,32</t>
+          <t>-7,24; 22,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 27,14</t>
+          <t>-3,5; 25,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 208,45</t>
+          <t>-32,67; 204,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 138,49</t>
+          <t>-45,04; 150,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 190,2</t>
+          <t>-33,3; 188,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 253,43</t>
+          <t>-12,37; 183,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>70,24%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 17,68</t>
+          <t>-12,85; 15,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 33,83</t>
+          <t>-8,2; 34,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 18,15</t>
+          <t>-29,97; 17,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 16,1</t>
+          <t>-5,86; 16,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 81,3</t>
+          <t>-42,25; 70,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,9; 449,67</t>
+          <t>-51,7; 440,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 111,79</t>
+          <t>-83,09; 123,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 527,01</t>
+          <t>-50,92; 474,12</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,84</t>
+          <t>-7,67; 5,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 12,31</t>
+          <t>-4,49; 11,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 16,8</t>
+          <t>0,82; 16,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 12,5</t>
+          <t>1,0; 14,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 33,56</t>
+          <t>-31,36; 29,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 53,88</t>
+          <t>-16,32; 45,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 80,58</t>
+          <t>2,56; 82,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 80,99</t>
+          <t>4,37; 86,71</t>
         </is>
       </c>
     </row>
